--- a/output/yearly_surface_area_iteration_91_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_91_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497640987125</v>
+        <v>10.84497644853494</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907221250073</v>
+        <v>37.78907234722345</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.239587497565227</v>
+        <v>7.749916377324321</v>
       </c>
       <c r="C2" t="n">
-        <v>6.698464586075987</v>
+        <v>9.514117001855839</v>
       </c>
       <c r="D2" t="n">
-        <v>28.33618398767569</v>
+        <v>20.53423498202629</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.61393647251952</v>
+        <v>18.17215000560846</v>
       </c>
       <c r="C3" t="n">
-        <v>32.91309178487432</v>
+        <v>19.35515598922587</v>
       </c>
       <c r="D3" t="n">
-        <v>79.03069019186825</v>
+        <v>71.5006853002952</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.00814138573701</v>
+        <v>33.13202152292136</v>
       </c>
       <c r="C4" t="n">
-        <v>64.51555038457914</v>
+        <v>68.10187474819274</v>
       </c>
       <c r="D4" t="n">
-        <v>97.46889382532758</v>
+        <v>97.12430038113695</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.89608327873264</v>
+        <v>42.85328729037328</v>
       </c>
       <c r="C5" t="n">
-        <v>99.32832397717107</v>
+        <v>124.5346962837079</v>
       </c>
       <c r="D5" t="n">
-        <v>65.48257187326226</v>
+        <v>68.57507714163971</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.11831811279092</v>
+        <v>43.35103337642641</v>
       </c>
       <c r="C6" t="n">
-        <v>133.0317226639641</v>
+        <v>124.0556034040355</v>
       </c>
       <c r="D6" t="n">
-        <v>43.31078172055229</v>
+        <v>44.75984133202059</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.29022177202533</v>
+        <v>32.69808903764427</v>
       </c>
       <c r="C7" t="n">
-        <v>117.6173019595849</v>
+        <v>98.2140403328509</v>
       </c>
       <c r="D7" t="n">
-        <v>38.08788393395925</v>
+        <v>38.26754376383641</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.10280577150543</v>
+        <v>17.60764507566654</v>
       </c>
       <c r="C8" t="n">
-        <v>71.34851440613694</v>
+        <v>65.75746123045136</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>37.60780930658255</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
         <v>34.39062207976576</v>
@@ -898,7 +898,7 @@
         <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.689809714369549</v>
+        <v>7.687243880127141</v>
       </c>
       <c r="C21" t="n">
-        <v>94.20016900102696</v>
+        <v>93.20783204654157</v>
       </c>
       <c r="D21" t="n">
-        <v>8.651035928665742</v>
+        <v>8.648149365143032</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.353871141885357</v>
+        <v>7.718500450788423</v>
       </c>
       <c r="C2" t="n">
-        <v>9.638798960295183</v>
+        <v>13.86816807019044</v>
       </c>
       <c r="D2" t="n">
-        <v>38.77903431774901</v>
+        <v>30.43908757017235</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.15742379004476</v>
+        <v>21.99605731364979</v>
       </c>
       <c r="C3" t="n">
-        <v>29.1922679857789</v>
+        <v>28.31851252899925</v>
       </c>
       <c r="D3" t="n">
-        <v>82.23609644623407</v>
+        <v>70.93127163183205</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.79117514309847</v>
+        <v>33.83397113145782</v>
       </c>
       <c r="C4" t="n">
-        <v>73.2707764110522</v>
+        <v>58.14695302713008</v>
       </c>
       <c r="D4" t="n">
-        <v>112.120496563507</v>
+        <v>108.6490366812903</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.53484118129882</v>
+        <v>45.84761778832605</v>
       </c>
       <c r="C5" t="n">
-        <v>107.6977231558751</v>
+        <v>123.7002107350981</v>
       </c>
       <c r="D5" t="n">
-        <v>81.58323422290995</v>
+        <v>83.96397240570847</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.57116584635595</v>
+        <v>50.15356321915257</v>
       </c>
       <c r="C6" t="n">
-        <v>145.1877227379481</v>
+        <v>158.994040702771</v>
       </c>
       <c r="D6" t="n">
-        <v>52.56866257159972</v>
+        <v>54.54099370943156</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.45287309576081</v>
+        <v>41.98051358129786</v>
       </c>
       <c r="C7" t="n">
-        <v>151.8125562462055</v>
+        <v>135.2838518975062</v>
       </c>
       <c r="D7" t="n">
-        <v>41.14210104187108</v>
+        <v>41.62119392154352</v>
       </c>
     </row>
     <row r="8">
@@ -1175,10 +1175,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.61179305066178</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="C8" t="n">
-        <v>111.1534750748239</v>
+        <v>95.71549242554278</v>
       </c>
       <c r="D8" t="n">
         <v>38.05254101660637</v>
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.42812411450962</v>
+        <v>12.53593643552752</v>
       </c>
       <c r="C9" t="n">
-        <v>60.68280734719958</v>
+        <v>58.79687000734145</v>
       </c>
       <c r="D9" t="n">
         <v>35.49999698556465</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>37.29659528433633</v>
+        <v>37.15424186722054</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1279,7 +1279,7 @@
         <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.869438018250128</v>
+        <v>7.867833516291556</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3026942372517</v>
+        <v>101.2983565222538</v>
       </c>
       <c r="D21" t="n">
-        <v>9.83679752281266</v>
+        <v>9.834791895364445</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.088218424661971</v>
+        <v>9.320712704119218</v>
       </c>
       <c r="C2" t="n">
-        <v>12.42696244035613</v>
+        <v>13.17996292951343</v>
       </c>
       <c r="D2" t="n">
-        <v>38.10162840181872</v>
+        <v>31.36389390757285</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.24716374175872</v>
+        <v>23.35086914551039</v>
       </c>
       <c r="C3" t="n">
-        <v>32.76092089071606</v>
+        <v>39.91295291615408</v>
       </c>
       <c r="D3" t="n">
-        <v>90.36987617591889</v>
+        <v>76.13944320286139</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.2551408965797</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="C4" t="n">
-        <v>72.17318247770427</v>
+        <v>63.06060028688537</v>
       </c>
       <c r="D4" t="n">
-        <v>122.2668590868978</v>
+        <v>115.2090748410674</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.44924920458011</v>
+        <v>48.03200643027521</v>
       </c>
       <c r="C5" t="n">
-        <v>119.4786956068369</v>
+        <v>114.9135687820892</v>
       </c>
       <c r="D5" t="n">
-        <v>98.3956636581366</v>
+        <v>98.59201319898595</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.05168244208915</v>
+        <v>54.86300695642451</v>
       </c>
       <c r="C6" t="n">
-        <v>155.1298817388555</v>
+        <v>175.6582262346563</v>
       </c>
       <c r="D6" t="n">
-        <v>62.26931163726245</v>
+        <v>65.77120569831082</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.6573386601514</v>
+        <v>49.40645321622073</v>
       </c>
       <c r="C7" t="n">
-        <v>176.0067466696639</v>
+        <v>174.5694680306466</v>
       </c>
       <c r="D7" t="n">
-        <v>45.75337000871835</v>
+        <v>46.17257627843174</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.95526587842792</v>
+        <v>33.96356182841841</v>
       </c>
       <c r="C8" t="n">
-        <v>150.4577444143449</v>
+        <v>131.0976796865978</v>
       </c>
       <c r="D8" t="n">
-        <v>39.72151211382594</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.75468624712531</v>
+        <v>18.08281096452199</v>
       </c>
       <c r="C9" t="n">
-        <v>92.41092965304799</v>
+        <v>84.86718029361549</v>
       </c>
       <c r="D9" t="n">
         <v>36.60937189136354</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>51.53193699591508</v>
+        <v>50.53546307610457</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.96083756948391</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>36.45032876327558</v>
       </c>
     </row>
     <row r="13">
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
         <v>31.65056423721292</v>
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.032396125266066</v>
+        <v>8.031943562265889</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4454467224084</v>
+        <v>109.4352310358727</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04454467224084</v>
+        <v>11.0439223981156</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.530585728649783</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="C2" t="n">
-        <v>8.549059008581224</v>
+        <v>8.962374792069131</v>
       </c>
       <c r="D2" t="n">
-        <v>31.3481859443049</v>
+        <v>25.82192811709961</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.35577788403162</v>
+        <v>26.73298998664065</v>
       </c>
       <c r="C3" t="n">
-        <v>49.86787463721674</v>
+        <v>56.2345084992573</v>
       </c>
       <c r="D3" t="n">
-        <v>96.85922850099031</v>
+        <v>83.05094704075893</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.26643884294516</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="C4" t="n">
-        <v>99.12804744550469</v>
+        <v>91.86605967719103</v>
       </c>
       <c r="D4" t="n">
-        <v>115.1707866806018</v>
+        <v>110.6400210255028</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.86967390170921</v>
+        <v>30.90050899116836</v>
       </c>
       <c r="C5" t="n">
-        <v>92.67698328089891</v>
+        <v>104.9488295839841</v>
       </c>
       <c r="D5" t="n">
-        <v>63.64179492779949</v>
+        <v>65.80163987714248</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.08936440328224</v>
+        <v>30.67176177607885</v>
       </c>
       <c r="C6" t="n">
-        <v>115.9247689174634</v>
+        <v>114.9587291764845</v>
       </c>
       <c r="D6" t="n">
-        <v>30.10823859384119</v>
+        <v>30.39000018496002</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>22.51736534460484</v>
       </c>
       <c r="C7" t="n">
-        <v>105.7597531876919</v>
+        <v>92.16549272698632</v>
       </c>
       <c r="D7" t="n">
-        <v>27.90716024091983</v>
+        <v>28.38625312059227</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>12.51728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>68.09402076655876</v>
+        <v>62.50296759087318</v>
       </c>
       <c r="D8" t="n">
         <v>26.95388322009618</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>39.2718716652809</v>
+        <v>38.49530923122167</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.972151211382595</v>
+        <v>5.065818153913542</v>
       </c>
       <c r="C2" t="n">
-        <v>4.241150082346221</v>
+        <v>4.123340357836604</v>
       </c>
       <c r="D2" t="n">
-        <v>21.42860714059513</v>
+        <v>18.5609220964902</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.58157985600839</v>
+        <v>28.62776305583699</v>
       </c>
       <c r="C3" t="n">
-        <v>42.33296100712246</v>
+        <v>46.35321785601315</v>
       </c>
       <c r="D3" t="n">
-        <v>100.3493415895877</v>
+        <v>85.32369297609029</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.45559735469531</v>
+        <v>34.86775146402972</v>
       </c>
       <c r="C4" t="n">
-        <v>114.9282949976529</v>
+        <v>117.6339916705571</v>
       </c>
       <c r="D4" t="n">
-        <v>132.4515097707542</v>
+        <v>123.4920802217978</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.52668410002858</v>
+        <v>34.28753857081986</v>
       </c>
       <c r="C5" t="n">
-        <v>133.7876683962341</v>
+        <v>137.3955912093411</v>
       </c>
       <c r="D5" t="n">
-        <v>82.61406931236911</v>
+        <v>83.39946747576656</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.28182801104362</v>
+        <v>35.94472869558847</v>
       </c>
       <c r="C6" t="n">
-        <v>135.4468220164112</v>
+        <v>141.6858286768997</v>
       </c>
       <c r="D6" t="n">
-        <v>37.71580155404972</v>
+        <v>38.31957639216151</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.30723027816702</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="C7" t="n">
-        <v>131.6307686900038</v>
+        <v>120.1924261878243</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>91.54306468249383</v>
+        <v>83.03131208667398</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>28.12216298814988</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>44.26405874137593</v>
+        <v>43.26562132615692</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2167,7 +2167,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.175773896789184</v>
+        <v>5.615596868291756</v>
       </c>
       <c r="C2" t="n">
-        <v>4.111559385385641</v>
+        <v>9.252972112526189</v>
       </c>
       <c r="D2" t="n">
-        <v>18.94282195344221</v>
+        <v>17.44958369528281</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.52557917913731</v>
+        <v>22.89926520155685</v>
       </c>
       <c r="C3" t="n">
-        <v>28.56394945506095</v>
+        <v>30.21328559819559</v>
       </c>
       <c r="D3" t="n">
-        <v>94.52757770340413</v>
+        <v>80.60639525718437</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.55617758888499</v>
+        <v>44.1207235765559</v>
       </c>
       <c r="C4" t="n">
-        <v>111.2526315929528</v>
+        <v>116.58744861783</v>
       </c>
       <c r="D4" t="n">
-        <v>149.3876394167159</v>
+        <v>135.7825797312636</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.32528695193774</v>
+        <v>42.53421928649306</v>
       </c>
       <c r="C5" t="n">
-        <v>171.1922559280376</v>
+        <v>177.6227033908542</v>
       </c>
       <c r="D5" t="n">
-        <v>106.519625910779</v>
+        <v>104.5315868096792</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.03781480104267</v>
+        <v>41.25794727097221</v>
       </c>
       <c r="C6" t="n">
-        <v>171.1902924326291</v>
+        <v>177.228040813747</v>
       </c>
       <c r="D6" t="n">
-        <v>51.2806095836279</v>
+        <v>51.96488773348793</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.69135567243478</v>
+        <v>29.76364514965055</v>
       </c>
       <c r="C7" t="n">
-        <v>162.9514656985898</v>
+        <v>160.3763414703505</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.2669375645639</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C8" t="n">
-        <v>129.2618114796563</v>
+        <v>117.6624623539802</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.70768553050848</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>73.44061876388687</v>
+        <v>68.55936917837174</v>
       </c>
       <c r="D9" t="n">
         <v>29.7312474754104</v>
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>40.57072387799944</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>14.46605242207675</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.87936820556466</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.087596529856219</v>
+        <v>3.363467634749572</v>
       </c>
       <c r="C2" t="n">
-        <v>1.944842202112931</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="D2" t="n">
-        <v>13.20941536064083</v>
+        <v>12.17858027118168</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.52696183746906</v>
+        <v>23.26251185212817</v>
       </c>
       <c r="C3" t="n">
-        <v>25.00511402716626</v>
+        <v>34.68514639103981</v>
       </c>
       <c r="D3" t="n">
-        <v>92.42663761631597</v>
+        <v>79.487202874343</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.24460371374025</v>
+        <v>48.47281114948201</v>
       </c>
       <c r="C4" t="n">
-        <v>108.6107485208246</v>
+        <v>114.0476673069435</v>
       </c>
       <c r="D4" t="n">
-        <v>160.8740875564036</v>
+        <v>145.0610772841002</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.42975311921541</v>
+        <v>44.05592822807562</v>
       </c>
       <c r="C5" t="n">
-        <v>205.3816197284328</v>
+        <v>213.5301256736813</v>
       </c>
       <c r="D5" t="n">
-        <v>112.8764422957771</v>
+        <v>110.274810879523</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.396291581813</v>
+        <v>35.22019888985433</v>
       </c>
       <c r="C6" t="n">
-        <v>206.5714979459799</v>
+        <v>212.0859748007342</v>
       </c>
       <c r="D6" t="n">
-        <v>50.27431818677493</v>
+        <v>50.91834468076083</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.084692344472483</v>
+        <v>10.12083708308037</v>
       </c>
       <c r="C7" t="n">
-        <v>169.7186526239631</v>
+        <v>162.3525995989993</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>34.2551408965797</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>93.37893288943536</v>
+        <v>86.20235717139117</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>12.18348900970292</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.541826921753</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.140610905885546</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C2" t="n">
-        <v>2.522109852210056</v>
+        <v>5.824709129296326</v>
       </c>
       <c r="D2" t="n">
-        <v>12.8815116274224</v>
+        <v>15.32606341099696</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.21218067730433</v>
+        <v>17.47020039707199</v>
       </c>
       <c r="C3" t="n">
-        <v>16.1301147807751</v>
+        <v>25.60398012675681</v>
       </c>
       <c r="D3" t="n">
-        <v>83.51236846175493</v>
+        <v>72.37934949559609</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.25361936952772</v>
+        <v>46.94128473085699</v>
       </c>
       <c r="C4" t="n">
-        <v>86.8758360965045</v>
+        <v>101.5402015548391</v>
       </c>
       <c r="D4" t="n">
-        <v>168.1743634851829</v>
+        <v>150.1023517454076</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.63363784652926</v>
+        <v>55.86144437164352</v>
       </c>
       <c r="C5" t="n">
-        <v>204.5962215650353</v>
+        <v>213.6773878293183</v>
       </c>
       <c r="D5" t="n">
-        <v>137.7392029058275</v>
+        <v>131.2105806725862</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.6139207769863</v>
+        <v>44.75984133202059</v>
       </c>
       <c r="C6" t="n">
-        <v>260.4684651614256</v>
+        <v>269.2433261419836</v>
       </c>
       <c r="D6" t="n">
-        <v>67.74353683614267</v>
+        <v>67.70328518026855</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.54677671800324</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="C7" t="n">
-        <v>226.910365134861</v>
+        <v>225.4730864958437</v>
       </c>
       <c r="D7" t="n">
-        <v>39.1059563032632</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>145.6177282324081</v>
+        <v>137.1894241914493</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>61.12655730951914</v>
+        <v>58.02030757328223</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3086,7 +3086,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3131,7 +3131,7 @@
         <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.153954463117502</v>
+        <v>3.07188856658827</v>
       </c>
       <c r="C2" t="n">
-        <v>1.994911335029519</v>
+        <v>3.200497515844602</v>
       </c>
       <c r="D2" t="n">
-        <v>10.06095047312131</v>
+        <v>11.32838675930394</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.46466976374501</v>
+        <v>16.67498475663207</v>
       </c>
       <c r="C3" t="n">
-        <v>13.41558237853267</v>
+        <v>24.74985962406209</v>
       </c>
       <c r="D3" t="n">
-        <v>77.47462008063705</v>
+        <v>69.64518213926873</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.85873580824224</v>
+        <v>42.41051907575796</v>
       </c>
       <c r="C4" t="n">
-        <v>69.44196036448963</v>
+        <v>87.60331114535138</v>
       </c>
       <c r="D4" t="n">
-        <v>170.7779583968454</v>
+        <v>151.7232172051191</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.66509483079416</v>
+        <v>62.34097921967247</v>
       </c>
       <c r="C5" t="n">
-        <v>194.8523756003857</v>
+        <v>210.8794068722149</v>
       </c>
       <c r="D5" t="n">
-        <v>154.4780012632356</v>
+        <v>145.1023106876786</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.57745724320893</v>
+        <v>52.60891422747383</v>
       </c>
       <c r="C6" t="n">
-        <v>293.8370878810704</v>
+        <v>304.7855382788308</v>
       </c>
       <c r="D6" t="n">
-        <v>82.55614619781855</v>
+        <v>81.59010645683969</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.86995163914969</v>
+        <v>17.90609637775757</v>
       </c>
       <c r="C7" t="n">
-        <v>280.1495613884613</v>
+        <v>282.006046297192</v>
       </c>
       <c r="D7" t="n">
-        <v>43.5375654402333</v>
+        <v>43.95677170994669</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>185.673034565678</v>
+        <v>177.3281790795801</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>69.55780659359074</v>
+        <v>66.45155685735384</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
         <v>25.33890824661018</v>
@@ -3428,7 +3428,7 @@
         <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.261365873507904</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C2" t="n">
-        <v>7.532950134685777</v>
+        <v>10.17090621599696</v>
       </c>
       <c r="D2" t="n">
-        <v>11.48644813968768</v>
+        <v>19.56917698875167</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.55378782065321</v>
+        <v>13.65611056607313</v>
       </c>
       <c r="C3" t="n">
-        <v>10.72068493037517</v>
+        <v>19.17353266394021</v>
       </c>
       <c r="D3" t="n">
-        <v>69.25248305757</v>
+        <v>63.62706871223578</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.47286790274425</v>
+        <v>37.12675293150163</v>
       </c>
       <c r="C4" t="n">
-        <v>53.3864584092373</v>
+        <v>76.18067660643975</v>
       </c>
       <c r="D4" t="n">
-        <v>169.9994324673777</v>
+        <v>151.3275728803076</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.39511421212629</v>
+        <v>63.24909584610077</v>
       </c>
       <c r="C5" t="n">
-        <v>166.062624173348</v>
+        <v>189.7963749235146</v>
       </c>
       <c r="D5" t="n">
-        <v>173.1557513365312</v>
+        <v>160.3930311813227</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.80137783523521</v>
+        <v>63.79887456047898</v>
       </c>
       <c r="C6" t="n">
-        <v>301.2433925619083</v>
+        <v>317.6258165026749</v>
       </c>
       <c r="D6" t="n">
-        <v>102.8027291025005</v>
+        <v>100.0253648471863</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.2845522699781</v>
+        <v>32.09922293805371</v>
       </c>
       <c r="C7" t="n">
-        <v>341.2339035466979</v>
+        <v>344.0485742147735</v>
       </c>
       <c r="D7" t="n">
-        <v>52.4007837141735</v>
+        <v>52.58044354405067</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>255.7698206489002</v>
+        <v>252.9325697836269</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>127.4671766762931</v>
+        <v>119.479677354541</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>48.54251523648354</v>
+        <v>47.54604131667303</v>
       </c>
       <c r="D10" t="n">
         <v>26.47773558353648</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
         <v>24.52209415667683</v>
@@ -3739,7 +3739,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.077599126364503</v>
+        <v>7.281622722398593</v>
       </c>
       <c r="C2" t="n">
-        <v>4.660356352059609</v>
+        <v>5.277875658030853</v>
       </c>
       <c r="D2" t="n">
-        <v>7.638978886744431</v>
+        <v>5.243514488382214</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.358157985600839</v>
+        <v>3.190680038802134</v>
       </c>
       <c r="C2" t="n">
-        <v>4.338343105066655</v>
+        <v>5.939573610693203</v>
       </c>
       <c r="D2" t="n">
-        <v>8.546113765468485</v>
+        <v>14.5593184539802</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.21079801897258</v>
+        <v>18.14269757448106</v>
       </c>
       <c r="C3" t="n">
-        <v>17.69600236904876</v>
+        <v>27.7343726449724</v>
       </c>
       <c r="D3" t="n">
-        <v>74.08759050098554</v>
+        <v>70.46985021083604</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.70406163932775</v>
+        <v>49.07265899677682</v>
       </c>
       <c r="C4" t="n">
-        <v>81.27300194836796</v>
+        <v>109.6445288533965</v>
       </c>
       <c r="D4" t="n">
-        <v>173.381553308508</v>
+        <v>155.1181007664046</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.57577148524092</v>
+        <v>37.11006322052944</v>
       </c>
       <c r="C5" t="n">
-        <v>250.8119947424539</v>
+        <v>273.9812405626786</v>
       </c>
       <c r="D5" t="n">
-        <v>155.386117889664</v>
+        <v>145.9613399288945</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.15349679922777</v>
+        <v>19.92456965768902</v>
       </c>
       <c r="C6" t="n">
-        <v>283.7741739125406</v>
+        <v>285.7465050503724</v>
       </c>
       <c r="D6" t="n">
-        <v>80.38255678061611</v>
+        <v>78.12846405166543</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>179.8394897070435</v>
+        <v>177.8632315783946</v>
       </c>
       <c r="D7" t="n">
-        <v>32.39865598784899</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>93.96307277346222</v>
+        <v>88.03822537833271</v>
       </c>
       <c r="D8" t="n">
         <v>24.53387512912779</v>
@@ -4302,7 +4302,7 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>37.05312185368311</v>
+        <v>36.27655941962388</v>
       </c>
       <c r="D9" t="n">
         <v>20.1906232855399</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
         <v>19.21771131063132</v>
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
         <v>9.105709956889166</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.198755004614362</v>
+        <v>7.39354196068273</v>
       </c>
       <c r="C2" t="n">
-        <v>7.858890372495717</v>
+        <v>6.877142668248906</v>
       </c>
       <c r="D2" t="n">
-        <v>9.714393533522189</v>
+        <v>13.25555750274043</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.78940726967245</v>
+        <v>15.46252634188726</v>
       </c>
       <c r="C3" t="n">
-        <v>11.92823460659875</v>
+        <v>13.50884841043611</v>
       </c>
       <c r="D3" t="n">
-        <v>9.552405162321465</v>
+        <v>7.539822368615503</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39901996282602</v>
+        <v>13.39894664310019</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1478103936186</v>
+        <v>70.14742654328923</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576355289744238</v>
+        <v>1.57634666389414</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.84452400983051</v>
+        <v>4.677046063031804</v>
       </c>
       <c r="C2" t="n">
-        <v>8.525497063679301</v>
+        <v>4.483641765295182</v>
       </c>
       <c r="D2" t="n">
-        <v>15.58524480491811</v>
+        <v>22.27781890476862</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.14622365467055</v>
+        <v>21.53463589265379</v>
       </c>
       <c r="C3" t="n">
-        <v>23.83683425911256</v>
+        <v>21.83406894244906</v>
       </c>
       <c r="D3" t="n">
-        <v>15.40362147963246</v>
+        <v>16.8516993433965</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.60956751334603</v>
+        <v>17.89333365760237</v>
       </c>
       <c r="C4" t="n">
+        <v>21.12230185687013</v>
+      </c>
+      <c r="D4" t="n">
         <v>19.01645303126072</v>
-      </c>
-      <c r="D4" t="n">
-        <v>20.07575880414303</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
         <v>16.54343056426301</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44471385254039</v>
+        <v>15.44310225897913</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16524570364639</v>
+        <v>86.15625470798882</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251518705797977</v>
+        <v>3.251179422942974</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.892048810261856</v>
+        <v>4.564145077043421</v>
       </c>
       <c r="C2" t="n">
-        <v>7.691011515069513</v>
+        <v>6.370560852857552</v>
       </c>
       <c r="D2" t="n">
-        <v>28.24389970347649</v>
+        <v>30.21426734589983</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.98146996680633</v>
+        <v>18.52067044061608</v>
       </c>
       <c r="C3" t="n">
-        <v>29.50151851261665</v>
+        <v>19.17353266394021</v>
       </c>
       <c r="D3" t="n">
-        <v>24.29334694158732</v>
+        <v>30.7630643125738</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.18535469412017</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="C4" t="n">
-        <v>42.94655332227672</v>
+        <v>40.86622993697772</v>
       </c>
       <c r="D4" t="n">
-        <v>23.29196428325558</v>
+        <v>23.18986252201391</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.43736075447534</v>
+        <v>15.58524480491812</v>
       </c>
       <c r="C5" t="n">
-        <v>22.2856728864026</v>
+        <v>24.54369260617026</v>
       </c>
       <c r="D5" t="n">
-        <v>29.67332436085985</v>
+        <v>29.30516897176729</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
         <v>36.6290068454485</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,7 +5274,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
         <v>32.11100391050467</v>
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74216276332367</v>
+        <v>16.73781255718266</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1271928562744</v>
+        <v>102.1006565988143</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022648828997101</v>
+        <v>5.0213437671548</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.51251335934584</v>
+        <v>4.710425484976196</v>
       </c>
       <c r="C2" t="n">
-        <v>5.060909415392308</v>
+        <v>11.75250176753857</v>
       </c>
       <c r="D2" t="n">
-        <v>40.52556348360408</v>
+        <v>33.7200883977652</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.9583089325319</v>
+        <v>16.94005663677871</v>
       </c>
       <c r="C3" t="n">
-        <v>29.68805057642355</v>
+        <v>22.36421270274234</v>
       </c>
       <c r="D3" t="n">
-        <v>40.35473938306514</v>
+        <v>46.88336161630643</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.92933952749001</v>
+        <v>33.93607289269949</v>
       </c>
       <c r="C4" t="n">
-        <v>59.78058120699678</v>
+        <v>44.83543590524759</v>
       </c>
       <c r="D4" t="n">
-        <v>29.85200244303276</v>
+        <v>32.83847895935156</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.73375075016664</v>
+        <v>31.1214022246239</v>
       </c>
       <c r="C5" t="n">
-        <v>53.6525120370882</v>
+        <v>51.81173509162543</v>
       </c>
       <c r="D5" t="n">
-        <v>31.09685853201772</v>
+        <v>30.75324683553134</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.74719211838983</v>
+        <v>13.52455637370406</v>
       </c>
       <c r="C6" t="n">
-        <v>24.43275511559037</v>
+        <v>26.28433128579986</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
         <v>39.46527596301753</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
         <v>41.93437143919824</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>46.86470840992573</v>
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07078097067416</v>
+        <v>18.06412777514927</v>
       </c>
       <c r="C21" t="n">
-        <v>117.89033299916</v>
+        <v>117.8469288188309</v>
       </c>
       <c r="D21" t="n">
-        <v>6.884107036447298</v>
+        <v>6.881572485771148</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.809982913732624</v>
+        <v>5.733406592801373</v>
       </c>
       <c r="C2" t="n">
-        <v>5.259222451650163</v>
+        <v>8.779769719079225</v>
       </c>
       <c r="D2" t="n">
-        <v>30.77386353732052</v>
+        <v>28.90167066532185</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.67360209830033</v>
+        <v>14.66731070144735</v>
       </c>
       <c r="C3" t="n">
-        <v>22.48202242725196</v>
+        <v>33.55613653115598</v>
       </c>
       <c r="D3" t="n">
-        <v>58.48761948050372</v>
+        <v>58.40417092564275</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.0840136964045</v>
+        <v>24.0704902127233</v>
       </c>
       <c r="C4" t="n">
-        <v>56.81963013098839</v>
+        <v>42.72958707963818</v>
       </c>
       <c r="D4" t="n">
-        <v>37.21609197258809</v>
+        <v>41.98934931063608</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.83130362578557</v>
+        <v>25.37817815478006</v>
       </c>
       <c r="C5" t="n">
-        <v>62.12008598621694</v>
+        <v>50.48637569089224</v>
       </c>
       <c r="D5" t="n">
-        <v>27.85709110800325</v>
+        <v>28.44613973055134</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.67298020349458</v>
+        <v>15.13462260866883</v>
       </c>
       <c r="C6" t="n">
-        <v>37.99756314516856</v>
+        <v>37.59504658642736</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>30.5510068084565</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="C7" t="n">
-        <v>18.08575620763474</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.66194429903638</v>
       </c>
     </row>
     <row r="8">
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
         <v>30.37527396939631</v>
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5871,7 +5871,7 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.47308888692249</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5916,7 +5916,7 @@
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.062540209840641</v>
+        <v>7.059787423180608</v>
       </c>
       <c r="C21" t="n">
-        <v>66.21131446725602</v>
+        <v>66.18550709231819</v>
       </c>
       <c r="D21" t="n">
-        <v>5.296905157380481</v>
+        <v>5.294840567385456</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.929756133650734</v>
+        <v>5.239587497565227</v>
       </c>
       <c r="C2" t="n">
-        <v>8.992808970900782</v>
+        <v>4.59850624669206</v>
       </c>
       <c r="D2" t="n">
-        <v>26.77225989481052</v>
+        <v>23.11034095796992</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.58939277991335</v>
+        <v>18.02488784997144</v>
       </c>
       <c r="C3" t="n">
-        <v>21.23520284285851</v>
+        <v>34.04210164475816</v>
       </c>
       <c r="D3" t="n">
-        <v>70.20477833068941</v>
+        <v>68.57016840311847</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.19735665074939</v>
+        <v>27.26117025152543</v>
       </c>
       <c r="C4" t="n">
-        <v>56.61542660850506</v>
+        <v>68.75277347610837</v>
       </c>
       <c r="D4" t="n">
-        <v>58.87442807597697</v>
+        <v>62.44798971943536</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.94897448157495</v>
+        <v>32.05406254365837</v>
       </c>
       <c r="C5" t="n">
-        <v>87.8173321448772</v>
+        <v>67.49515466696822</v>
       </c>
       <c r="D5" t="n">
-        <v>35.80924751240241</v>
+        <v>38.11635461738242</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.32708621643021</v>
+        <v>26.08307300642926</v>
       </c>
       <c r="C6" t="n">
-        <v>74.3045567436241</v>
+        <v>63.15484806649307</v>
       </c>
       <c r="D6" t="n">
-        <v>33.12711278440013</v>
+        <v>33.20761609614837</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.36038352291659</v>
+        <v>13.05528097107408</v>
       </c>
       <c r="C7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.94436884268997</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>32.75797564760332</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>22.19731559302038</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
         <v>31.17343485294896</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.285045023213623</v>
+        <v>7.282054578229351</v>
       </c>
       <c r="C21" t="n">
-        <v>75.58234211584136</v>
+        <v>75.55131624912951</v>
       </c>
       <c r="D21" t="n">
-        <v>6.374414395311921</v>
+        <v>6.371797755950682</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.213080309550564</v>
+        <v>5.384886157793755</v>
       </c>
       <c r="C2" t="n">
-        <v>9.191122007158638</v>
+        <v>4.004548885622739</v>
       </c>
       <c r="D2" t="n">
-        <v>27.40156017323272</v>
+        <v>21.51892792938584</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.69876768571225</v>
+        <v>18.09851892778995</v>
       </c>
       <c r="C3" t="n">
-        <v>29.5800583289564</v>
+        <v>24.24916829489622</v>
       </c>
       <c r="D3" t="n">
-        <v>75.33441008537899</v>
+        <v>71.14725612676635</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.22586839190155</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="C4" t="n">
-        <v>54.63720498444773</v>
+        <v>78.50349167468769</v>
       </c>
       <c r="D4" t="n">
-        <v>80.82630674293564</v>
+        <v>82.77900292668257</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.82749980815561</v>
+        <v>37.42913122440965</v>
       </c>
       <c r="C5" t="n">
-        <v>97.51209072431446</v>
+        <v>101.488168926514</v>
       </c>
       <c r="D5" t="n">
-        <v>48.47379289718628</v>
+        <v>51.54175447295756</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.3032054763588</v>
+        <v>35.82397372796611</v>
       </c>
       <c r="C6" t="n">
-        <v>109.5247556334784</v>
+        <v>86.90332503222342</v>
       </c>
       <c r="D6" t="n">
-        <v>37.31328499530853</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>22.63713856452295</v>
       </c>
       <c r="C7" t="n">
-        <v>77.25372684718151</v>
+        <v>68.51028179315941</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>39.13737222979909</v>
+        <v>39.55461500410399</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>26.40312275801371</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
         <v>32.72655972106742</v>
@@ -6493,7 +6493,7 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6633,7 +6633,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.494780657257285</v>
+        <v>7.491685407152837</v>
       </c>
       <c r="C21" t="n">
-        <v>85.25312997630162</v>
+        <v>84.28146083046941</v>
       </c>
       <c r="D21" t="n">
-        <v>7.494780657257285</v>
+        <v>7.491685407152837</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_91_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_91_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497644853494</v>
+        <v>10.84497631076243</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907234722345</v>
+        <v>37.78907186715829</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.749916377324321</v>
+        <v>4.313799412460485</v>
       </c>
       <c r="C2" t="n">
-        <v>9.514117001855839</v>
+        <v>6.115306449753382</v>
       </c>
       <c r="D2" t="n">
-        <v>20.53423498202629</v>
+        <v>26.19891923553038</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.17215000560846</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C3" t="n">
-        <v>19.35515598922587</v>
+        <v>30.13474578185584</v>
       </c>
       <c r="D3" t="n">
-        <v>71.5006853002952</v>
+        <v>55.03677630007619</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.13202152292136</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="C4" t="n">
-        <v>68.10187474819274</v>
+        <v>81.70693443364505</v>
       </c>
       <c r="D4" t="n">
-        <v>97.12430038113695</v>
+        <v>65.56209343730625</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.85328729037328</v>
+        <v>39.14718970684157</v>
       </c>
       <c r="C5" t="n">
-        <v>124.5346962837079</v>
+        <v>112.7782675253524</v>
       </c>
       <c r="D5" t="n">
-        <v>68.57507714163971</v>
+        <v>54.21701696703012</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.35103337642641</v>
+        <v>37.07177506006381</v>
       </c>
       <c r="C6" t="n">
-        <v>124.0556034040355</v>
+        <v>131.663166364244</v>
       </c>
       <c r="D6" t="n">
-        <v>44.75984133202059</v>
+        <v>42.2642386678252</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.69808903764427</v>
+        <v>26.05067533218911</v>
       </c>
       <c r="C7" t="n">
-        <v>98.2140403328509</v>
+        <v>138.0386359556228</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>38.44720359371359</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.60764507566654</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C8" t="n">
-        <v>65.75746123045136</v>
+        <v>106.2300103380261</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>35.38218726105504</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>57.90937008270233</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.687243880127141</v>
+        <v>7.675988691988819</v>
       </c>
       <c r="C21" t="n">
-        <v>93.20783204654157</v>
+        <v>94.99036006336165</v>
       </c>
       <c r="D21" t="n">
-        <v>8.648149365143032</v>
+        <v>7.675988691988819</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.718500450788423</v>
+        <v>5.175773896789184</v>
       </c>
       <c r="C2" t="n">
-        <v>13.86816807019044</v>
+        <v>8.23293624781375</v>
       </c>
       <c r="D2" t="n">
-        <v>30.43908757017235</v>
+        <v>23.60219655779757</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.99605731364979</v>
+        <v>14.16171063376024</v>
       </c>
       <c r="C3" t="n">
-        <v>28.31851252899925</v>
+        <v>26.73789872516188</v>
       </c>
       <c r="D3" t="n">
-        <v>70.93127163183205</v>
+        <v>61.6684820422634</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.83397113145782</v>
+        <v>28.35876418487337</v>
       </c>
       <c r="C4" t="n">
-        <v>58.14695302713008</v>
+        <v>77.63562670413351</v>
       </c>
       <c r="D4" t="n">
-        <v>108.6490366812903</v>
+        <v>76.21896476690537</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.84761778832605</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="C5" t="n">
-        <v>123.7002107350981</v>
+        <v>130.8669689760999</v>
       </c>
       <c r="D5" t="n">
-        <v>83.96397240570847</v>
+        <v>63.07728999785758</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.15356321915257</v>
+        <v>44.67933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>158.994040702771</v>
+        <v>152.6342790746601</v>
       </c>
       <c r="D6" t="n">
-        <v>54.54099370943156</v>
+        <v>48.82525857530663</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.98051358129786</v>
+        <v>34.2551408965797</v>
       </c>
       <c r="C7" t="n">
-        <v>135.2838518975062</v>
+        <v>162.113053159163</v>
       </c>
       <c r="D7" t="n">
-        <v>41.62119392154352</v>
+        <v>41.26187426178919</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.70215489718149</v>
+        <v>20.02765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>95.71549242554278</v>
+        <v>143.2811686963007</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.53593643552752</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>58.79687000734145</v>
+        <v>91.52342972840887</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>37.15424186722054</v>
+        <v>49.82369599052563</v>
       </c>
       <c r="D10" t="n">
         <v>35.58835427894688</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.867833516291556</v>
+        <v>7.854210252403283</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2983565222538</v>
+        <v>103.0865095627931</v>
       </c>
       <c r="D21" t="n">
-        <v>9.834791895364445</v>
+        <v>8.835986533953694</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.320712704119218</v>
+        <v>5.819800390775092</v>
       </c>
       <c r="C2" t="n">
-        <v>13.17996292951343</v>
+        <v>7.261987768313657</v>
       </c>
       <c r="D2" t="n">
-        <v>31.36389390757285</v>
+        <v>23.98802340556657</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.35086914551039</v>
+        <v>15.34471661737765</v>
       </c>
       <c r="C3" t="n">
-        <v>39.91295291615408</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D3" t="n">
-        <v>76.13944320286139</v>
+        <v>64.4811892149305</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.66729500591412</v>
+        <v>27.37603473292231</v>
       </c>
       <c r="C4" t="n">
-        <v>63.06060028688537</v>
+        <v>71.76477543273759</v>
       </c>
       <c r="D4" t="n">
-        <v>115.2090748410674</v>
+        <v>85.28049607710342</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.03200643027521</v>
+        <v>41.94517066394498</v>
       </c>
       <c r="C5" t="n">
-        <v>114.9135687820892</v>
+        <v>135.9229696529709</v>
       </c>
       <c r="D5" t="n">
-        <v>98.59201319898595</v>
+        <v>73.16474765899356</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.86300695642451</v>
+        <v>49.50953672516665</v>
       </c>
       <c r="C6" t="n">
-        <v>175.6582262346563</v>
+        <v>174.7726898054257</v>
       </c>
       <c r="D6" t="n">
-        <v>65.77120569831082</v>
+        <v>55.02401357992099</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.40645321622073</v>
+        <v>42.04040019125691</v>
       </c>
       <c r="C7" t="n">
-        <v>174.5694680306466</v>
+        <v>186.5467900224577</v>
       </c>
       <c r="D7" t="n">
-        <v>46.17257627843174</v>
+        <v>45.09461729916874</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.96356182841841</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="C8" t="n">
-        <v>131.0976796865978</v>
+        <v>175.5757594274996</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.38771789438203</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.08281096452199</v>
+        <v>14.31093628480575</v>
       </c>
       <c r="C9" t="n">
-        <v>84.86718029361549</v>
+        <v>127.3562391857132</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>50.53546307610457</v>
+        <v>73.73907006597793</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>43.71329827929347</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>36.45032876327558</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>31.65056423721292</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.031943562265889</v>
+        <v>8.016992350203591</v>
       </c>
       <c r="C21" t="n">
-        <v>109.4352310358727</v>
+        <v>111.2357688590748</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0439223981156</v>
+        <v>10.02124043775449</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.499971623368884</v>
+        <v>5.341689258806895</v>
       </c>
       <c r="C2" t="n">
-        <v>8.962374792069131</v>
+        <v>4.93720920465721</v>
       </c>
       <c r="D2" t="n">
-        <v>25.82192811709961</v>
+        <v>19.80872342858789</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.73298998664065</v>
+        <v>18.64338890364693</v>
       </c>
       <c r="C3" t="n">
-        <v>56.2345084992573</v>
+        <v>43.52578446778234</v>
       </c>
       <c r="D3" t="n">
-        <v>83.05094704075893</v>
+        <v>68.87941892995622</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.07499804061703</v>
+        <v>20.15233512507428</v>
       </c>
       <c r="C4" t="n">
-        <v>91.86605967719103</v>
+        <v>107.1175102626652</v>
       </c>
       <c r="D4" t="n">
-        <v>110.6400210255028</v>
+        <v>81.96218883674922</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.90050899116836</v>
+        <v>27.88163480060942</v>
       </c>
       <c r="C5" t="n">
-        <v>104.9488295839841</v>
+        <v>104.4334120392545</v>
       </c>
       <c r="D5" t="n">
-        <v>65.80163987714248</v>
+        <v>52.52350217720437</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.67176177607885</v>
+        <v>26.08307300642926</v>
       </c>
       <c r="C6" t="n">
-        <v>114.9587291764845</v>
+        <v>122.8480537278119</v>
       </c>
       <c r="D6" t="n">
-        <v>30.39000018496002</v>
+        <v>29.66547037922588</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.51736534460484</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>92.16549272698632</v>
+        <v>123.4263031256132</v>
       </c>
       <c r="D7" t="n">
-        <v>28.38625312059227</v>
+        <v>27.66761380108361</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>62.50296759087318</v>
+        <v>93.87962421860124</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>26.70353755551324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>38.49530923122167</v>
+        <v>56.24530772400399</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
         <v>23.66110142005238</v>
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.065818153913542</v>
+        <v>3.29965403397353</v>
       </c>
       <c r="C2" t="n">
-        <v>4.123340357836604</v>
+        <v>2.766565030567512</v>
       </c>
       <c r="D2" t="n">
-        <v>18.5609220964902</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.62776305583699</v>
+        <v>19.02627050830318</v>
       </c>
       <c r="C3" t="n">
-        <v>46.35321785601315</v>
+        <v>31.79880814055419</v>
       </c>
       <c r="D3" t="n">
-        <v>85.32369297609029</v>
+        <v>69.01195487002954</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.86775146402972</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="C4" t="n">
-        <v>117.6339916705571</v>
+        <v>110.7548855068997</v>
       </c>
       <c r="D4" t="n">
-        <v>123.4920802217978</v>
+        <v>95.95013012685776</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.28753857081986</v>
+        <v>30.65507206510666</v>
       </c>
       <c r="C5" t="n">
-        <v>137.3955912093411</v>
+        <v>149.1765636603029</v>
       </c>
       <c r="D5" t="n">
-        <v>83.39946747576656</v>
+        <v>65.0407854063512</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.94472869558847</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="C6" t="n">
-        <v>141.6858286768997</v>
+        <v>147.0392989081575</v>
       </c>
       <c r="D6" t="n">
-        <v>38.31957639216151</v>
+        <v>35.58246379272141</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.31963314542373</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>120.1924261878243</v>
+        <v>148.6984525283346</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>30.18285141936394</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>83.03131208667398</v>
+        <v>121.1673016581413</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>43.26562132615692</v>
+        <v>61.68124476241858</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>35.73070769606267</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.615596868291756</v>
+        <v>3.503857556456866</v>
       </c>
       <c r="C2" t="n">
-        <v>9.252972112526189</v>
+        <v>8.827875356587318</v>
       </c>
       <c r="D2" t="n">
-        <v>17.44958369528281</v>
+        <v>12.32486067911446</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.89926520155685</v>
+        <v>15.07473599870977</v>
       </c>
       <c r="C3" t="n">
-        <v>30.21328559819559</v>
+        <v>20.70996782108647</v>
       </c>
       <c r="D3" t="n">
-        <v>80.60639525718437</v>
+        <v>65.10459900712723</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.1207235765559</v>
+        <v>31.68983414538279</v>
       </c>
       <c r="C4" t="n">
-        <v>116.58744861783</v>
+        <v>94.69938355164733</v>
       </c>
       <c r="D4" t="n">
-        <v>135.7825797312636</v>
+        <v>106.6452896169225</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.53421928649306</v>
+        <v>35.31837366027901</v>
       </c>
       <c r="C5" t="n">
-        <v>177.6227033908542</v>
+        <v>176.0764507566655</v>
       </c>
       <c r="D5" t="n">
-        <v>104.5315868096792</v>
+        <v>81.41142837466676</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.25794727097221</v>
+        <v>35.783722072092</v>
       </c>
       <c r="C6" t="n">
-        <v>177.228040813747</v>
+        <v>191.074610434444</v>
       </c>
       <c r="D6" t="n">
-        <v>51.96488773348793</v>
+        <v>45.32336451425826</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.76364514965055</v>
+        <v>25.09248957284423</v>
       </c>
       <c r="C7" t="n">
-        <v>160.3763414703505</v>
+        <v>180.2586959767568</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.27108553955913</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C8" t="n">
-        <v>117.6624623539802</v>
+        <v>156.7998345837793</v>
       </c>
       <c r="D8" t="n">
-        <v>29.70768553050848</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>68.55936917837174</v>
+        <v>99.17811657842124</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>40.57072387799944</v>
+        <v>51.24723016168351</v>
       </c>
       <c r="D10" t="n">
         <v>30.46363126277853</v>
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2537,7 +2537,7 @@
         <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.363467634749572</v>
+        <v>2.067560665143783</v>
       </c>
       <c r="C2" t="n">
-        <v>4.311835917051991</v>
+        <v>4.119413367019616</v>
       </c>
       <c r="D2" t="n">
-        <v>12.17858027118168</v>
+        <v>8.602073384610552</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.26251185212817</v>
+        <v>15.10909716835841</v>
       </c>
       <c r="C3" t="n">
-        <v>34.68514639103981</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D3" t="n">
-        <v>79.487202874343</v>
+        <v>63.28345701574941</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.47281114948201</v>
+        <v>35.05919226635785</v>
       </c>
       <c r="C4" t="n">
-        <v>114.0476673069435</v>
+        <v>88.48393883606077</v>
       </c>
       <c r="D4" t="n">
-        <v>145.0610772841002</v>
+        <v>114.328447150358</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.05592822807562</v>
+        <v>37.38004383919731</v>
       </c>
       <c r="C5" t="n">
-        <v>213.5301256736813</v>
+        <v>203.0499689308466</v>
       </c>
       <c r="D5" t="n">
-        <v>110.274810879523</v>
+        <v>86.24653581808231</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.22019888985433</v>
+        <v>30.10823859384119</v>
       </c>
       <c r="C6" t="n">
-        <v>212.0859748007342</v>
+        <v>232.4935643289127</v>
       </c>
       <c r="D6" t="n">
-        <v>50.91834468076083</v>
+        <v>44.92084795551706</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>162.3525995989993</v>
+        <v>196.1885342258656</v>
       </c>
       <c r="D7" t="n">
-        <v>34.2551408965797</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>86.20235717139117</v>
+        <v>120.6666103289755</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>30.95155987178918</v>
+        <v>39.04999668412111</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2834,7 +2834,7 @@
         <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.491495746929157</v>
+        <v>2.259983215176157</v>
       </c>
       <c r="C2" t="n">
-        <v>5.824709129296326</v>
+        <v>8.943721585688444</v>
       </c>
       <c r="D2" t="n">
-        <v>15.32606341099696</v>
+        <v>12.96397843457913</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.47020039707199</v>
+        <v>11.19683256693487</v>
       </c>
       <c r="C3" t="n">
-        <v>25.60398012675681</v>
+        <v>21.81934272688536</v>
       </c>
       <c r="D3" t="n">
-        <v>72.37934949559609</v>
+        <v>56.26886966890594</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.94128473085699</v>
+        <v>32.49388551516093</v>
       </c>
       <c r="C4" t="n">
-        <v>101.5402015548391</v>
+        <v>79.89462817160542</v>
       </c>
       <c r="D4" t="n">
-        <v>150.1023517454076</v>
+        <v>119.03789088763</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.86144437164352</v>
+        <v>44.1541029985003</v>
       </c>
       <c r="C5" t="n">
-        <v>213.6773878293183</v>
+        <v>185.9184714917398</v>
       </c>
       <c r="D5" t="n">
-        <v>131.2105806725862</v>
+        <v>104.9733732765902</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.75984133202059</v>
+        <v>38.40007970390975</v>
       </c>
       <c r="C6" t="n">
-        <v>269.2433261419836</v>
+        <v>275.0798162437308</v>
       </c>
       <c r="D6" t="n">
-        <v>67.70328518026855</v>
+        <v>57.27810630887167</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>16.88802400845363</v>
       </c>
       <c r="C7" t="n">
-        <v>225.4730864958437</v>
+        <v>260.0875470521777</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>37.54890444432775</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>137.1894241914493</v>
+        <v>178.3295617379119</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>58.02030757328223</v>
+        <v>79.43124325520091</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.13520344574558</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.07188856658827</v>
+        <v>1.534471661737765</v>
       </c>
       <c r="C2" t="n">
-        <v>3.200497515844602</v>
+        <v>4.613232462255762</v>
       </c>
       <c r="D2" t="n">
-        <v>11.32838675930394</v>
+        <v>9.804714322312895</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.67498475663207</v>
+        <v>9.930378028456488</v>
       </c>
       <c r="C3" t="n">
-        <v>24.74985962406209</v>
+        <v>28.03380569476767</v>
       </c>
       <c r="D3" t="n">
-        <v>69.64518213926873</v>
+        <v>54.2317431825938</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.41051907575796</v>
+        <v>28.75440850968483</v>
       </c>
       <c r="C4" t="n">
-        <v>87.60331114535138</v>
+        <v>70.96072406295946</v>
       </c>
       <c r="D4" t="n">
-        <v>151.7232172051191</v>
+        <v>120.2248238620644</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.34097921967247</v>
+        <v>47.73748211900116</v>
       </c>
       <c r="C5" t="n">
-        <v>210.8794068722149</v>
+        <v>177.4018101573987</v>
       </c>
       <c r="D5" t="n">
-        <v>145.1023106876786</v>
+        <v>118.055161435679</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.60891422747383</v>
+        <v>44.63908636439822</v>
       </c>
       <c r="C6" t="n">
-        <v>304.7855382788308</v>
+        <v>295.8496706747763</v>
       </c>
       <c r="D6" t="n">
-        <v>81.59010645683969</v>
+        <v>67.62278186852032</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.90609637775757</v>
+        <v>15.75017841923158</v>
       </c>
       <c r="C7" t="n">
-        <v>282.006046297192</v>
+        <v>314.344815675082</v>
       </c>
       <c r="D7" t="n">
-        <v>43.95677170994669</v>
+        <v>42.10028680121597</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>177.3281790795801</v>
+        <v>225.144201014921</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>66.45155685735384</v>
+        <v>91.74530470956864</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.412955930589413</v>
+        <v>3.103304493124168</v>
       </c>
       <c r="C2" t="n">
-        <v>10.17090621599696</v>
+        <v>12.18054376659018</v>
       </c>
       <c r="D2" t="n">
-        <v>19.56917698875167</v>
+        <v>9.088038498212724</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.65611056607313</v>
+        <v>7.682175785731291</v>
       </c>
       <c r="C3" t="n">
-        <v>19.17353266394021</v>
+        <v>23.37050409959532</v>
       </c>
       <c r="D3" t="n">
-        <v>63.62706871223578</v>
+        <v>50.13294651736337</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.12675293150163</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="C4" t="n">
-        <v>76.18067660643975</v>
+        <v>69.60787572650736</v>
       </c>
       <c r="D4" t="n">
-        <v>151.3275728803076</v>
+        <v>119.5611624139936</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.24909584610077</v>
+        <v>46.43666641087414</v>
       </c>
       <c r="C5" t="n">
-        <v>189.7963749235146</v>
+        <v>156.8096520608218</v>
       </c>
       <c r="D5" t="n">
-        <v>160.3930311813227</v>
+        <v>129.6643280383975</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.79887456047898</v>
+        <v>51.6831261423691</v>
       </c>
       <c r="C6" t="n">
-        <v>317.6258165026749</v>
+        <v>294.2396044398116</v>
       </c>
       <c r="D6" t="n">
-        <v>100.0253648471863</v>
+        <v>81.79136473621028</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.09922293805371</v>
+        <v>28.68568617038755</v>
       </c>
       <c r="C7" t="n">
-        <v>344.0485742147735</v>
+        <v>361.0563714431452</v>
       </c>
       <c r="D7" t="n">
-        <v>52.58044354405067</v>
+        <v>49.10702016642545</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>252.9325697836269</v>
+        <v>300.08100328008</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>119.479677354541</v>
+        <v>161.7468612654789</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>47.54604131667303</v>
+        <v>60.21549543997811</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.281622722398593</v>
+        <v>4.316744655573225</v>
       </c>
       <c r="C2" t="n">
-        <v>5.277875658030853</v>
+        <v>13.78471951532946</v>
       </c>
       <c r="D2" t="n">
-        <v>5.243514488382214</v>
+        <v>7.829437941368313</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.190680038802134</v>
+        <v>2.216786316189298</v>
       </c>
       <c r="C2" t="n">
-        <v>5.939573610693203</v>
+        <v>6.91935781953152</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5593184539802</v>
+        <v>6.68864710903352</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.14269757448106</v>
+        <v>10.82867717784232</v>
       </c>
       <c r="C3" t="n">
-        <v>27.7343726449724</v>
+        <v>34.09609776849172</v>
       </c>
       <c r="D3" t="n">
-        <v>70.46985021083604</v>
+        <v>54.12375093512666</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.07265899677682</v>
+        <v>34.56144618030471</v>
       </c>
       <c r="C4" t="n">
-        <v>109.6445288533965</v>
+        <v>98.28570791526093</v>
       </c>
       <c r="D4" t="n">
-        <v>155.1181007664046</v>
+        <v>122.9177578148134</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.11006322052944</v>
+        <v>30.38509144643879</v>
       </c>
       <c r="C5" t="n">
-        <v>273.9812405626786</v>
+        <v>243.0071004936918</v>
       </c>
       <c r="D5" t="n">
-        <v>145.9613399288945</v>
+        <v>117.7851808170111</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.92456965768902</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="C6" t="n">
-        <v>285.7465050503724</v>
+        <v>295.4874057719093</v>
       </c>
       <c r="D6" t="n">
-        <v>78.12846405166543</v>
+        <v>68.18630505075798</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>177.8632315783946</v>
+        <v>211.0404134957113</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>88.03822537833271</v>
+        <v>119.1645363414778</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>25.03456645829366</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>36.27655941962388</v>
+        <v>45.92812110007426</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>23.06125357275758</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>16.34806277111788</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.39354196068273</v>
+        <v>6.433392705929348</v>
       </c>
       <c r="C2" t="n">
-        <v>6.877142668248906</v>
+        <v>6.69748283837174</v>
       </c>
       <c r="D2" t="n">
-        <v>13.25555750274043</v>
+        <v>9.420850969952392</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.46252634188726</v>
+        <v>9.174432296186444</v>
       </c>
       <c r="C3" t="n">
-        <v>13.50884841043611</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D3" t="n">
-        <v>7.539822368615503</v>
+        <v>9.714393533522189</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39894664310019</v>
+        <v>13.39755056250005</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14742654328923</v>
+        <v>70.14011765073556</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57634666389414</v>
+        <v>1.576182419117653</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.677046063031804</v>
+        <v>4.975497365122835</v>
       </c>
       <c r="C2" t="n">
-        <v>4.483641765295182</v>
+        <v>4.14592055503428</v>
       </c>
       <c r="D2" t="n">
-        <v>22.27781890476862</v>
+        <v>19.87351877706818</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.53463589265379</v>
+        <v>16.94987411382118</v>
       </c>
       <c r="C3" t="n">
-        <v>21.83406894244906</v>
+        <v>29.34443887993716</v>
       </c>
       <c r="D3" t="n">
-        <v>16.8516993433965</v>
+        <v>15.28090301660161</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.89333365760237</v>
+        <v>10.79726125130642</v>
       </c>
       <c r="C4" t="n">
-        <v>21.12230185687013</v>
+        <v>53.46303473016855</v>
       </c>
       <c r="D4" t="n">
-        <v>19.01645303126072</v>
+        <v>20.16509784522949</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44310225897913</v>
+        <v>15.43923694368366</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15625470798882</v>
+        <v>86.13469031739305</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251179422942974</v>
+        <v>3.250365672354455</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.564145077043421</v>
+        <v>4.249004063980196</v>
       </c>
       <c r="C2" t="n">
-        <v>6.370560852857552</v>
+        <v>5.846307578789756</v>
       </c>
       <c r="D2" t="n">
-        <v>30.21426734589983</v>
+        <v>16.88704226074939</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.52067044061608</v>
+        <v>17.11677122354314</v>
       </c>
       <c r="C3" t="n">
-        <v>19.17353266394021</v>
+        <v>21.44627859927157</v>
       </c>
       <c r="D3" t="n">
-        <v>30.7630643125738</v>
+        <v>27.63128913602648</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.29418982057133</v>
+        <v>23.26643884294516</v>
       </c>
       <c r="C4" t="n">
-        <v>40.86622993697772</v>
+        <v>64.54107582488956</v>
       </c>
       <c r="D4" t="n">
-        <v>23.18986252201391</v>
+        <v>23.30472700341079</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.58524480491812</v>
+        <v>9.842020735074275</v>
       </c>
       <c r="C5" t="n">
-        <v>24.54369260617026</v>
+        <v>58.56125055832225</v>
       </c>
       <c r="D5" t="n">
-        <v>29.30516897176729</v>
+        <v>29.91876128692155</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
         <v>31.27455486648638</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73781255718266</v>
+        <v>16.72880987293723</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1006565988143</v>
+        <v>102.0457402249171</v>
       </c>
       <c r="D21" t="n">
-        <v>5.0213437671548</v>
+        <v>4.182202468234307</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.710425484976196</v>
+        <v>4.675082567623311</v>
       </c>
       <c r="C2" t="n">
-        <v>11.75250176753857</v>
+        <v>6.714172549343935</v>
       </c>
       <c r="D2" t="n">
-        <v>33.7200883977652</v>
+        <v>17.66262294710436</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.94005663677871</v>
+        <v>15.69323705238526</v>
       </c>
       <c r="C3" t="n">
-        <v>22.36421270274234</v>
+        <v>22.15313694632928</v>
       </c>
       <c r="D3" t="n">
-        <v>46.88336161630643</v>
+        <v>34.31699100194726</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.93607289269949</v>
+        <v>28.33323874456295</v>
       </c>
       <c r="C4" t="n">
-        <v>44.83543590524759</v>
+        <v>58.4660210310103</v>
       </c>
       <c r="D4" t="n">
-        <v>32.83847895935156</v>
+        <v>31.44734246243383</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.1214022246239</v>
+        <v>22.33476027161494</v>
       </c>
       <c r="C5" t="n">
-        <v>51.81173509162543</v>
+        <v>91.32708018755955</v>
       </c>
       <c r="D5" t="n">
-        <v>30.75324683553134</v>
+        <v>31.29320807286709</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.52455637370406</v>
+        <v>9.579894098040377</v>
       </c>
       <c r="C6" t="n">
-        <v>26.28433128579986</v>
+        <v>53.81646390369741</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.72499713628642</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06412777514927</v>
+        <v>18.04920615811357</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8469288188309</v>
+        <v>117.7495830315028</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881572485771148</v>
+        <v>6.016402052704523</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.733406592801373</v>
+        <v>5.190500112352886</v>
       </c>
       <c r="C2" t="n">
-        <v>8.779769719079225</v>
+        <v>10.36529226143782</v>
       </c>
       <c r="D2" t="n">
-        <v>28.90167066532185</v>
+        <v>15.56855509394592</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.66731070144735</v>
+        <v>14.1273494641116</v>
       </c>
       <c r="C3" t="n">
-        <v>33.55613653115598</v>
+        <v>22.85017781634451</v>
       </c>
       <c r="D3" t="n">
-        <v>58.40417092564275</v>
+        <v>37.73347301272616</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.0704902127233</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="C4" t="n">
-        <v>42.72958707963818</v>
+        <v>46.99233561147783</v>
       </c>
       <c r="D4" t="n">
-        <v>41.98934931063608</v>
+        <v>35.78666731520473</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.37817815478006</v>
+        <v>19.73312885536089</v>
       </c>
       <c r="C5" t="n">
-        <v>50.48637569089224</v>
+        <v>74.51465075233293</v>
       </c>
       <c r="D5" t="n">
-        <v>28.44613973055134</v>
+        <v>28.397052345339</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.13462260866883</v>
+        <v>10.82769543013807</v>
       </c>
       <c r="C6" t="n">
-        <v>37.59504658642736</v>
+        <v>67.82404014789091</v>
       </c>
       <c r="D6" t="n">
-        <v>30.5510068084565</v>
+        <v>30.75226508782709</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.168320825782709</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>18.98405535702057</v>
+        <v>31.91956310817654</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.059787423180608</v>
+        <v>7.052150887176659</v>
       </c>
       <c r="C21" t="n">
-        <v>66.18550709231819</v>
+        <v>66.99543342817825</v>
       </c>
       <c r="D21" t="n">
-        <v>5.294840567385456</v>
+        <v>4.407594304485412</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.239587497565227</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C2" t="n">
-        <v>4.59850624669206</v>
+        <v>9.476810589094461</v>
       </c>
       <c r="D2" t="n">
-        <v>23.11034095796992</v>
+        <v>16.91354944876405</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.02488784997144</v>
+        <v>16.66025854106837</v>
       </c>
       <c r="C3" t="n">
-        <v>34.04210164475816</v>
+        <v>34.23354244708628</v>
       </c>
       <c r="D3" t="n">
-        <v>68.57016840311847</v>
+        <v>41.6899162608408</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.26117025152543</v>
+        <v>25.55096575072749</v>
       </c>
       <c r="C4" t="n">
-        <v>68.75277347610837</v>
+        <v>53.51408561078939</v>
       </c>
       <c r="D4" t="n">
-        <v>62.44798971943536</v>
+        <v>46.91575929054657</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.05406254365837</v>
+        <v>27.243498792849</v>
       </c>
       <c r="C5" t="n">
-        <v>67.49515466696822</v>
+        <v>82.24591392327655</v>
       </c>
       <c r="D5" t="n">
-        <v>38.11635461738242</v>
+        <v>35.66198535676539</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.08307300642926</v>
+        <v>19.84406634594078</v>
       </c>
       <c r="C6" t="n">
-        <v>63.15484806649307</v>
+        <v>97.12724562424971</v>
       </c>
       <c r="D6" t="n">
-        <v>33.20761609614837</v>
+        <v>33.32837106377072</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.05528097107408</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>39.94436884268997</v>
+        <v>71.0854060213988</v>
       </c>
       <c r="D7" t="n">
-        <v>32.75797564760332</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>22.86490403190821</v>
+        <v>32.71183350550372</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
         <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>32.76190263842031</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.282054578229351</v>
+        <v>7.273677405775917</v>
       </c>
       <c r="C21" t="n">
-        <v>75.55131624912951</v>
+        <v>76.37361276064713</v>
       </c>
       <c r="D21" t="n">
-        <v>6.371797755950682</v>
+        <v>5.455258054331938</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.384886157793755</v>
+        <v>3.575525138866883</v>
       </c>
       <c r="C2" t="n">
-        <v>4.004548885622739</v>
+        <v>6.625815255961724</v>
       </c>
       <c r="D2" t="n">
-        <v>21.51892792938584</v>
+        <v>26.64070570244145</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.09851892778995</v>
+        <v>16.36573422979433</v>
       </c>
       <c r="C3" t="n">
-        <v>24.24916829489622</v>
+        <v>35.83869994352981</v>
       </c>
       <c r="D3" t="n">
-        <v>71.14725612676635</v>
+        <v>45.54818473853077</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.63878326476196</v>
+        <v>29.6095107600838</v>
       </c>
       <c r="C4" t="n">
-        <v>78.50349167468769</v>
+        <v>72.49225048158448</v>
       </c>
       <c r="D4" t="n">
-        <v>82.77900292668257</v>
+        <v>57.29185077673112</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.42913122440965</v>
+        <v>33.25670348136071</v>
       </c>
       <c r="C5" t="n">
-        <v>101.488168926514</v>
+        <v>91.84249773228912</v>
       </c>
       <c r="D5" t="n">
-        <v>51.54175447295756</v>
+        <v>44.17864669110647</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.82397372796611</v>
+        <v>29.22270216461057</v>
       </c>
       <c r="C6" t="n">
-        <v>86.90332503222342</v>
+        <v>115.9247689174634</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>37.43403996293088</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.63713856452295</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="C7" t="n">
-        <v>68.51028179315941</v>
+        <v>108.4546506358494</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>39.55461500410399</v>
+        <v>66.42504966933919</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.62976760897448</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>26.73593522975338</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.84673385161303</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.491685407152837</v>
+        <v>7.482378602292337</v>
       </c>
       <c r="C21" t="n">
-        <v>84.28146083046941</v>
+        <v>86.04735392636186</v>
       </c>
       <c r="D21" t="n">
-        <v>7.491685407152837</v>
+        <v>6.547081277005795</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_91_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_91_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497631076243</v>
+        <v>10.84497658505562</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907186715829</v>
+        <v>37.78907282292663</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.313799412460485</v>
+        <v>1.229148125717006</v>
       </c>
       <c r="C2" t="n">
-        <v>6.115306449753382</v>
+        <v>3.00414797499524</v>
       </c>
       <c r="D2" t="n">
-        <v>26.19891923553038</v>
+        <v>13.36158625479909</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.10280577150543</v>
+        <v>9.758572180213296</v>
       </c>
       <c r="C3" t="n">
-        <v>30.13474578185584</v>
+        <v>34.04701038327939</v>
       </c>
       <c r="D3" t="n">
-        <v>55.03677630007619</v>
+        <v>74.2692138262712</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.43908757017236</v>
+        <v>14.0517548908846</v>
       </c>
       <c r="C4" t="n">
-        <v>81.70693443364505</v>
+        <v>96.34577445166923</v>
       </c>
       <c r="D4" t="n">
-        <v>65.56209343730625</v>
+        <v>97.25192758268904</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.14718970684157</v>
+        <v>12.51728322914684</v>
       </c>
       <c r="C5" t="n">
-        <v>112.7782675253524</v>
+        <v>91.10618695410402</v>
       </c>
       <c r="D5" t="n">
-        <v>54.21701696703012</v>
+        <v>59.29756133650736</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.07177506006381</v>
+        <v>9.338384162795663</v>
       </c>
       <c r="C6" t="n">
-        <v>131.663166364244</v>
+        <v>46.73217246985243</v>
       </c>
       <c r="D6" t="n">
-        <v>42.2642386678252</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.05067533218911</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="C7" t="n">
-        <v>138.0386359556228</v>
+        <v>26.29022177202533</v>
       </c>
       <c r="D7" t="n">
-        <v>38.44720359371359</v>
+        <v>29.40432548989622</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.26832022289564</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>106.2300103380261</v>
+        <v>27.03733177495716</v>
       </c>
       <c r="D8" t="n">
-        <v>35.38218726105504</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>57.90937008270233</v>
+        <v>32.28280975874785</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.675988691988819</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.99036006336165</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.675988691988819</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.175773896789184</v>
+        <v>1.375428533649781</v>
       </c>
       <c r="C2" t="n">
-        <v>8.23293624781375</v>
+        <v>4.760494617892784</v>
       </c>
       <c r="D2" t="n">
-        <v>23.60219655779757</v>
+        <v>15.15327581504952</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.16171063376024</v>
+        <v>6.764241682260523</v>
       </c>
       <c r="C3" t="n">
-        <v>26.73789872516188</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D3" t="n">
-        <v>61.6684820422634</v>
+        <v>67.72586537746621</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.35876418487337</v>
+        <v>16.85955332503048</v>
       </c>
       <c r="C4" t="n">
-        <v>77.63562670413351</v>
+        <v>89.97717709422018</v>
       </c>
       <c r="D4" t="n">
-        <v>76.21896476690537</v>
+        <v>112.6948189704914</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.99425804915732</v>
+        <v>16.93514789825748</v>
       </c>
       <c r="C5" t="n">
-        <v>130.8669689760999</v>
+        <v>140.7089897111741</v>
       </c>
       <c r="D5" t="n">
-        <v>63.07728999785758</v>
+        <v>81.33779729684825</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.67933802027235</v>
+        <v>13.20254312671111</v>
       </c>
       <c r="C6" t="n">
-        <v>152.6342790746601</v>
+        <v>98.89831848271095</v>
       </c>
       <c r="D6" t="n">
-        <v>48.82525857530663</v>
+        <v>42.18373535607696</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.2551408965797</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>162.113053159163</v>
+        <v>47.66974152740813</v>
       </c>
       <c r="D7" t="n">
-        <v>41.26187426178919</v>
+        <v>31.91956310817654</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.02765316663493</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>143.2811686963007</v>
+        <v>31.96079651175491</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>91.52342972840887</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>49.82369599052563</v>
+        <v>35.16129402759952</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.854210252403283</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103.0865095627931</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.835986533953694</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.819800390775092</v>
+        <v>0.7176575718044184</v>
       </c>
       <c r="C2" t="n">
-        <v>7.261987768313657</v>
+        <v>1.946805697521425</v>
       </c>
       <c r="D2" t="n">
-        <v>23.98802340556657</v>
+        <v>10.20428563794135</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.34471661737765</v>
+        <v>6.533530971762523</v>
       </c>
       <c r="C3" t="n">
-        <v>28.9321048441535</v>
+        <v>21.10757564130643</v>
       </c>
       <c r="D3" t="n">
-        <v>64.4811892149305</v>
+        <v>66.91101478294136</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.37603473292231</v>
+        <v>18.49318150489717</v>
       </c>
       <c r="C4" t="n">
-        <v>71.76477543273759</v>
+        <v>83.1363590910284</v>
       </c>
       <c r="D4" t="n">
-        <v>85.28049607710342</v>
+        <v>121.973316523328</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.94517066394498</v>
+        <v>17.15604113171301</v>
       </c>
       <c r="C5" t="n">
-        <v>135.9229696529709</v>
+        <v>165.6699250916493</v>
       </c>
       <c r="D5" t="n">
-        <v>73.16474765899356</v>
+        <v>92.82424543653593</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.50953672516665</v>
+        <v>11.35096695650162</v>
       </c>
       <c r="C6" t="n">
-        <v>174.7726898054257</v>
+        <v>133.8770074373206</v>
       </c>
       <c r="D6" t="n">
-        <v>55.02401357992099</v>
+        <v>42.42524529132167</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.04040019125691</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>186.5467900224577</v>
+        <v>48.68781389671206</v>
       </c>
       <c r="D7" t="n">
-        <v>45.09461729916874</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.12078032981814</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>175.5757594274996</v>
+        <v>36.63391558396972</v>
       </c>
       <c r="D8" t="n">
-        <v>39.38771789438203</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.31093628480575</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>127.3562391857132</v>
+        <v>26.84687272033327</v>
       </c>
       <c r="D9" t="n">
-        <v>36.27655941962388</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>73.73907006597793</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>43.71329827929347</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.016992350203591</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111.2357688590748</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.02124043775449</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.341689258806895</v>
+        <v>0.5497787143782138</v>
       </c>
       <c r="C2" t="n">
-        <v>4.93720920465721</v>
+        <v>4.723188205131405</v>
       </c>
       <c r="D2" t="n">
-        <v>19.80872342858789</v>
+        <v>10.0943298950657</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.64338890364693</v>
+        <v>4.408047192068179</v>
       </c>
       <c r="C3" t="n">
-        <v>43.52578446778234</v>
+        <v>13.35176877775662</v>
       </c>
       <c r="D3" t="n">
-        <v>68.87941892995622</v>
+        <v>59.78352645010952</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.15233512507428</v>
+        <v>15.80024755214817</v>
       </c>
       <c r="C4" t="n">
-        <v>107.1175102626652</v>
+        <v>67.0042808148448</v>
       </c>
       <c r="D4" t="n">
-        <v>81.96218883674922</v>
+        <v>127.7420660334822</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.88163480060942</v>
+        <v>22.40839134943345</v>
       </c>
       <c r="C5" t="n">
-        <v>104.4334120392545</v>
+        <v>160.8593613408399</v>
       </c>
       <c r="D5" t="n">
-        <v>52.52350217720437</v>
+        <v>115.3798989416064</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.08307300642926</v>
+        <v>16.7446888436336</v>
       </c>
       <c r="C6" t="n">
-        <v>122.8480537278119</v>
+        <v>201.2582793705962</v>
       </c>
       <c r="D6" t="n">
-        <v>29.66547037922588</v>
+        <v>58.68691426446584</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>123.4263031256132</v>
+        <v>117.4376421297077</v>
       </c>
       <c r="D7" t="n">
-        <v>27.66761380108361</v>
+        <v>37.90822410408209</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>93.87962421860124</v>
+        <v>50.15258147144831</v>
       </c>
       <c r="D8" t="n">
-        <v>26.70353755551324</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>56.24530772400399</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.29965403397353</v>
+        <v>0.2974695543867835</v>
       </c>
       <c r="C2" t="n">
-        <v>2.766565030567512</v>
+        <v>2.211877577668064</v>
       </c>
       <c r="D2" t="n">
-        <v>14.05273663858884</v>
+        <v>8.097455064627692</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.02627050830318</v>
+        <v>3.303581024790517</v>
       </c>
       <c r="C3" t="n">
-        <v>31.79880814055419</v>
+        <v>16.22828955119978</v>
       </c>
       <c r="D3" t="n">
-        <v>69.01195487002954</v>
+        <v>55.07113746972483</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.9165768073348</v>
+        <v>13.19665264048563</v>
       </c>
       <c r="C4" t="n">
-        <v>110.7548855068997</v>
+        <v>52.03361007278519</v>
       </c>
       <c r="D4" t="n">
-        <v>95.95013012685776</v>
+        <v>129.3374060528833</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.65507206510666</v>
+        <v>24.22462460229005</v>
       </c>
       <c r="C5" t="n">
-        <v>149.1765636603029</v>
+        <v>151.3854959948582</v>
       </c>
       <c r="D5" t="n">
-        <v>65.0407854063512</v>
+        <v>131.5787360616788</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.79251674370121</v>
+        <v>20.76985443104552</v>
       </c>
       <c r="C6" t="n">
-        <v>147.0392989081575</v>
+        <v>232.2923060495421</v>
       </c>
       <c r="D6" t="n">
-        <v>35.58246379272141</v>
+        <v>72.8554971321558</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>9.162651323735481</v>
       </c>
       <c r="C7" t="n">
-        <v>148.6984525283346</v>
+        <v>180.6779022464702</v>
       </c>
       <c r="D7" t="n">
-        <v>30.18285141936394</v>
+        <v>43.11835917051991</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>121.1673016581413</v>
+        <v>79.44302422765189</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>61.68124476241858</v>
+        <v>45.37343364717482</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>35.73070769606267</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.503857556456866</v>
+        <v>1.447096116059799</v>
       </c>
       <c r="C2" t="n">
-        <v>8.827875356587318</v>
+        <v>14.60153360526281</v>
       </c>
       <c r="D2" t="n">
-        <v>12.32486067911446</v>
+        <v>18.58644753680061</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.07473599870977</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C3" t="n">
-        <v>20.70996782108647</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="D3" t="n">
-        <v>65.10459900712723</v>
+        <v>49.71079500453725</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.68983414538279</v>
+        <v>9.929396280752242</v>
       </c>
       <c r="C4" t="n">
-        <v>94.69938355164733</v>
+        <v>46.53287768589032</v>
       </c>
       <c r="D4" t="n">
-        <v>106.6452896169225</v>
+        <v>126.4147431373405</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.31837366027901</v>
+        <v>22.5311098124643</v>
       </c>
       <c r="C5" t="n">
-        <v>176.0764507566655</v>
+        <v>124.0929098167969</v>
       </c>
       <c r="D5" t="n">
-        <v>81.41142837466676</v>
+        <v>146.6731070144735</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.783722072092</v>
+        <v>26.24407962992574</v>
       </c>
       <c r="C6" t="n">
-        <v>191.074610434444</v>
+        <v>239.4973524510094</v>
       </c>
       <c r="D6" t="n">
-        <v>45.32336451425826</v>
+        <v>93.82660984257193</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.09248957284423</v>
+        <v>15.63040519931347</v>
       </c>
       <c r="C7" t="n">
-        <v>180.2586959767568</v>
+        <v>251.70342165791</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>52.22112388429633</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.10004045484194</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>156.7998345837793</v>
+        <v>151.0418842983718</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>43.14290286312608</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>99.17811657842124</v>
+        <v>68.78124415953151</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>42.59999638267758</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>51.24723016168351</v>
+        <v>42.42131830050468</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>42.57152569925444</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.067560665143783</v>
+        <v>0.9601492547533805</v>
       </c>
       <c r="C2" t="n">
-        <v>4.119413367019616</v>
+        <v>7.476008767839461</v>
       </c>
       <c r="D2" t="n">
-        <v>8.602073384610552</v>
+        <v>13.38220295658827</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.10909716835841</v>
+        <v>3.848451000647497</v>
       </c>
       <c r="C3" t="n">
-        <v>27.95035713990669</v>
+        <v>30.52744486355457</v>
       </c>
       <c r="D3" t="n">
-        <v>63.28345701574941</v>
+        <v>57.01008918561228</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.05919226635785</v>
+        <v>15.71090851106171</v>
       </c>
       <c r="C4" t="n">
-        <v>88.48393883606077</v>
+        <v>66.20022944506667</v>
       </c>
       <c r="D4" t="n">
-        <v>114.328447150358</v>
+        <v>132.6301878529271</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.38004383919731</v>
+        <v>16.44427404613408</v>
       </c>
       <c r="C5" t="n">
-        <v>203.0499689308466</v>
+        <v>194.0424337443821</v>
       </c>
       <c r="D5" t="n">
-        <v>86.24653581808231</v>
+        <v>136.7329115089746</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.10823859384119</v>
+        <v>9.700649065662736</v>
       </c>
       <c r="C6" t="n">
-        <v>232.4935643289127</v>
+        <v>226.8180808506619</v>
       </c>
       <c r="D6" t="n">
-        <v>44.92084795551706</v>
+        <v>77.04166934306421</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.964919124554372</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>196.1885342258656</v>
+        <v>106.1789594574053</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>37.96811071404115</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>120.6666103289755</v>
+        <v>50.65327280061418</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>35.83379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.259983215176157</v>
+        <v>0.4525856916577796</v>
       </c>
       <c r="C2" t="n">
-        <v>8.943721585688444</v>
+        <v>4.288273972150068</v>
       </c>
       <c r="D2" t="n">
-        <v>12.96397843457913</v>
+        <v>9.227446672215772</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.19683256693487</v>
+        <v>3.593196597543326</v>
       </c>
       <c r="C3" t="n">
-        <v>21.81934272688536</v>
+        <v>30.13965452037708</v>
       </c>
       <c r="D3" t="n">
-        <v>56.26886966890594</v>
+        <v>54.34464416858219</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.49388551516093</v>
+        <v>10.86107485208246</v>
       </c>
       <c r="C4" t="n">
-        <v>79.89462817160542</v>
+        <v>68.6506717148667</v>
       </c>
       <c r="D4" t="n">
-        <v>119.03789088763</v>
+        <v>125.9425224915978</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.1541029985003</v>
+        <v>15.78159434576748</v>
       </c>
       <c r="C5" t="n">
-        <v>185.9184714917398</v>
+        <v>144.0223882130071</v>
       </c>
       <c r="D5" t="n">
-        <v>104.9733732765902</v>
+        <v>137.1010668980671</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.40007970390975</v>
+        <v>9.620145753914496</v>
       </c>
       <c r="C6" t="n">
-        <v>275.0798162437308</v>
+        <v>219.1300145787051</v>
       </c>
       <c r="D6" t="n">
-        <v>57.27810630887167</v>
+        <v>83.40143097117505</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.88802400845363</v>
+        <v>3.593196597543325</v>
       </c>
       <c r="C7" t="n">
-        <v>260.0875470521777</v>
+        <v>149.1775454080071</v>
       </c>
       <c r="D7" t="n">
-        <v>37.54890444432775</v>
+        <v>38.38731698375453</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>178.3295617379119</v>
+        <v>57.57950285407543</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>79.43124325520091</v>
+        <v>29.06562253193106</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>21.63281066307846</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>34.16482010778901</v>
+        <v>18.93300447639974</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.534471661737765</v>
+        <v>0.7981608835526568</v>
       </c>
       <c r="C2" t="n">
-        <v>4.613232462255762</v>
+        <v>6.591454086313084</v>
       </c>
       <c r="D2" t="n">
-        <v>9.804714322312895</v>
+        <v>11.66316272645211</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.930378028456488</v>
+        <v>2.478912953223196</v>
       </c>
       <c r="C3" t="n">
-        <v>28.03380569476767</v>
+        <v>22.2709466708389</v>
       </c>
       <c r="D3" t="n">
-        <v>54.2317431825938</v>
+        <v>49.11683764346792</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.75440850968483</v>
+        <v>8.908378668335558</v>
       </c>
       <c r="C4" t="n">
-        <v>70.96072406295946</v>
+        <v>72.61987768313656</v>
       </c>
       <c r="D4" t="n">
-        <v>120.2248238620644</v>
+        <v>125.0491320807332</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.73748211900116</v>
+        <v>16.29701189049706</v>
       </c>
       <c r="C5" t="n">
-        <v>177.4018101573987</v>
+        <v>134.5730665596316</v>
       </c>
       <c r="D5" t="n">
-        <v>118.055161435679</v>
+        <v>152.0972630804371</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.63908636439822</v>
+        <v>15.57739082328414</v>
       </c>
       <c r="C6" t="n">
-        <v>295.8496706747763</v>
+        <v>227.6633656240184</v>
       </c>
       <c r="D6" t="n">
-        <v>67.62278186852032</v>
+        <v>106.666888066416</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.75017841923158</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>314.344815675082</v>
+        <v>238.9475737366312</v>
       </c>
       <c r="D7" t="n">
-        <v>42.10028680121597</v>
+        <v>52.22112388429633</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>225.144201014921</v>
+        <v>128.7611201504904</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>91.74530470956864</v>
+        <v>50.25468323268996</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>23.74062298409636</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>34.73423377625215</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.76963344686726</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.103304493124168</v>
+        <v>0.3544109212330985</v>
       </c>
       <c r="C2" t="n">
-        <v>12.18054376659018</v>
+        <v>8.767006998924016</v>
       </c>
       <c r="D2" t="n">
-        <v>9.088038498212724</v>
+        <v>9.498409038587891</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.682175785731291</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C3" t="n">
-        <v>23.37050409959532</v>
+        <v>24.06754496961056</v>
       </c>
       <c r="D3" t="n">
-        <v>50.13294651736337</v>
+        <v>47.06007620307086</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.0832529328785</v>
+        <v>6.738716241950106</v>
       </c>
       <c r="C4" t="n">
-        <v>69.60787572650736</v>
+        <v>63.46900733185205</v>
       </c>
       <c r="D4" t="n">
-        <v>119.5611624139936</v>
+        <v>121.7052994000686</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.43666641087414</v>
+        <v>15.14345833800705</v>
       </c>
       <c r="C5" t="n">
-        <v>156.8096520608218</v>
+        <v>134.3030859409637</v>
       </c>
       <c r="D5" t="n">
-        <v>129.6643280383975</v>
+        <v>160.4175748739288</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.6831261423691</v>
+        <v>18.87802660496192</v>
       </c>
       <c r="C6" t="n">
-        <v>294.2396044398116</v>
+        <v>221.9476304898934</v>
       </c>
       <c r="D6" t="n">
-        <v>81.79136473621028</v>
+        <v>128.4832855501886</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.68568617038755</v>
+        <v>12.6360747013607</v>
       </c>
       <c r="C7" t="n">
-        <v>361.0563714431452</v>
+        <v>285.7789027246125</v>
       </c>
       <c r="D7" t="n">
-        <v>49.10702016642545</v>
+        <v>68.33062196328224</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>300.08100328008</v>
+        <v>220.7214276072891</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>161.7468612654789</v>
+        <v>102.2843663146582</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>26.07031028627404</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>60.21549543997811</v>
+        <v>42.13661146627311</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.316744655573225</v>
+        <v>3.392920065876976</v>
       </c>
       <c r="C2" t="n">
-        <v>13.78471951532946</v>
+        <v>2.376811191981528</v>
       </c>
       <c r="D2" t="n">
-        <v>7.829437941368313</v>
+        <v>15.6834195753428</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.216786316189298</v>
+        <v>0.2454369260617026</v>
       </c>
       <c r="C2" t="n">
-        <v>6.91935781953152</v>
+        <v>20.68444238077605</v>
       </c>
       <c r="D2" t="n">
-        <v>6.68864710903352</v>
+        <v>15.28777525053133</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.82867717784232</v>
+        <v>1.899681807717578</v>
       </c>
       <c r="C3" t="n">
-        <v>34.09609776849172</v>
+        <v>28.96646601380214</v>
       </c>
       <c r="D3" t="n">
-        <v>54.12375093512666</v>
+        <v>44.40444866308323</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.56144618030471</v>
+        <v>5.819800390775091</v>
       </c>
       <c r="C4" t="n">
-        <v>98.28570791526093</v>
+        <v>61.72051467058848</v>
       </c>
       <c r="D4" t="n">
-        <v>122.9177578148134</v>
+        <v>116.9320420620206</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.38509144643879</v>
+        <v>13.10633185169492</v>
       </c>
       <c r="C5" t="n">
-        <v>243.0071004936918</v>
+        <v>125.982774147472</v>
       </c>
       <c r="D5" t="n">
-        <v>117.7851808170111</v>
+        <v>166.8480223367455</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.7912318963607</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="C6" t="n">
-        <v>295.4874057719093</v>
+        <v>216.9161735056285</v>
       </c>
       <c r="D6" t="n">
-        <v>68.18630505075798</v>
+        <v>144.9059611468292</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>211.0404134957113</v>
+        <v>304.8228446915921</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>85.63785224144927</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>119.1645363414778</v>
+        <v>293.6554645557847</v>
       </c>
       <c r="D8" t="n">
-        <v>25.03456645829366</v>
+        <v>43.81049130201391</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>45.92812110007426</v>
+        <v>176.1687350408646</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>23.06125357275758</v>
+        <v>76.15907815694632</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>22.91890015564179</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.34806277111788</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.433392705929348</v>
+        <v>2.863758053287946</v>
       </c>
       <c r="C2" t="n">
-        <v>6.69748283837174</v>
+        <v>6.805475085838889</v>
       </c>
       <c r="D2" t="n">
-        <v>9.420850969952392</v>
+        <v>34.36215139634261</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.174432296186444</v>
+        <v>5.610688129770522</v>
       </c>
       <c r="C3" t="n">
-        <v>34.73423377625215</v>
+        <v>4.692754026299753</v>
       </c>
       <c r="D3" t="n">
-        <v>9.714393533522189</v>
+        <v>13.69047173572177</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39755056250005</v>
+        <v>11.67825367694724</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14011765073556</v>
+        <v>59.94836887499583</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576182419117653</v>
+        <v>0.7785502451298159</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.975497365122835</v>
+        <v>2.317906329726719</v>
       </c>
       <c r="C2" t="n">
-        <v>4.14592055503428</v>
+        <v>7.251188543566941</v>
       </c>
       <c r="D2" t="n">
-        <v>19.87351877706818</v>
+        <v>26.73986222057037</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.94987411382118</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C3" t="n">
-        <v>29.34443887993716</v>
+        <v>19.26679869584365</v>
       </c>
       <c r="D3" t="n">
-        <v>15.28090301660161</v>
+        <v>40.48727532313846</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.79726125130642</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C4" t="n">
-        <v>53.46303473016855</v>
+        <v>8.219191779954297</v>
       </c>
       <c r="D4" t="n">
-        <v>20.16509784522949</v>
+        <v>21.50518346152638</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.58292145661112</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43923694368366</v>
+        <v>13.62889563598296</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13469031739305</v>
+        <v>73.75637638296656</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250365672354455</v>
+        <v>1.60339948658623</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.249004063980196</v>
+        <v>1.77598159698248</v>
       </c>
       <c r="C2" t="n">
-        <v>5.846307578789756</v>
+        <v>4.580834788015617</v>
       </c>
       <c r="D2" t="n">
-        <v>16.88704226074939</v>
+        <v>24.5947434867911</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.11677122354314</v>
+        <v>8.246680715673207</v>
       </c>
       <c r="C3" t="n">
-        <v>21.44627859927157</v>
+        <v>25.11310627463341</v>
       </c>
       <c r="D3" t="n">
-        <v>27.63128913602648</v>
+        <v>53.16654692348601</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.26643884294516</v>
+        <v>12.67338111412208</v>
       </c>
       <c r="C4" t="n">
-        <v>64.54107582488956</v>
+        <v>33.36175048571511</v>
       </c>
       <c r="D4" t="n">
-        <v>23.30472700341079</v>
+        <v>37.72660077879643</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.842020735074275</v>
+        <v>6.945865007546185</v>
       </c>
       <c r="C5" t="n">
-        <v>58.56125055832225</v>
+        <v>11.29009859883832</v>
       </c>
       <c r="D5" t="n">
-        <v>29.91876128692155</v>
+        <v>27.68528525976006</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72880987293723</v>
+        <v>14.84086658066352</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0457402249171</v>
+        <v>87.39621430835182</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182202468234307</v>
+        <v>2.47347776344392</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.675082567623311</v>
+        <v>2.3237968159522</v>
       </c>
       <c r="C2" t="n">
-        <v>6.714172549343935</v>
+        <v>5.243514488382214</v>
       </c>
       <c r="D2" t="n">
-        <v>17.66262294710436</v>
+        <v>22.61554011502952</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.69323705238526</v>
+        <v>7.063674732055801</v>
       </c>
       <c r="C3" t="n">
-        <v>22.15313694632928</v>
+        <v>20.63633674326795</v>
       </c>
       <c r="D3" t="n">
-        <v>34.31699100194726</v>
+        <v>60.50511101273093</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.33323874456295</v>
+        <v>14.74094177926586</v>
       </c>
       <c r="C4" t="n">
-        <v>58.4660210310103</v>
+        <v>51.05088062083414</v>
       </c>
       <c r="D4" t="n">
-        <v>31.44734246243383</v>
+        <v>55.50506995500192</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.33476027161494</v>
+        <v>13.35176877775663</v>
       </c>
       <c r="C5" t="n">
-        <v>91.32708018755955</v>
+        <v>40.47254910757476</v>
       </c>
       <c r="D5" t="n">
-        <v>31.29320807286709</v>
+        <v>35.44109212330986</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.579894098040377</v>
+        <v>7.205046401467343</v>
       </c>
       <c r="C6" t="n">
-        <v>53.81646390369741</v>
+        <v>14.6516027381794</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>33.93214590188251</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04920615811357</v>
+        <v>16.08758975715632</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7495830315028</v>
+        <v>101.6058300451978</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016402052704523</v>
+        <v>3.386861001506594</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.190500112352886</v>
+        <v>1.994911335029519</v>
       </c>
       <c r="C2" t="n">
-        <v>10.36529226143782</v>
+        <v>9.197994241088367</v>
       </c>
       <c r="D2" t="n">
-        <v>15.56855509394592</v>
+        <v>24.21873411606457</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.1273494641116</v>
+        <v>7.588909753827844</v>
       </c>
       <c r="C3" t="n">
-        <v>22.85017781634451</v>
+        <v>20.469439633546</v>
       </c>
       <c r="D3" t="n">
-        <v>37.73347301272616</v>
+        <v>64.2357522888688</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.47965802121596</v>
+        <v>14.28148385367835</v>
       </c>
       <c r="C4" t="n">
-        <v>46.99233561147783</v>
+        <v>51.40823678517997</v>
       </c>
       <c r="D4" t="n">
-        <v>35.78666731520473</v>
+        <v>71.85411447382405</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.73312885536089</v>
+        <v>18.01507037292897</v>
       </c>
       <c r="C5" t="n">
-        <v>74.51465075233293</v>
+        <v>70.09678608322227</v>
       </c>
       <c r="D5" t="n">
-        <v>28.397052345339</v>
+        <v>47.34478303730243</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.82769543013807</v>
+        <v>12.67927160034756</v>
       </c>
       <c r="C6" t="n">
-        <v>67.82404014789091</v>
+        <v>40.65417243286043</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>37.63529824230149</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>31.91956310817654</v>
+        <v>19.76258128648829</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.052150887176659</v>
+        <v>17.36375283478234</v>
       </c>
       <c r="C21" t="n">
-        <v>66.99543342817825</v>
+        <v>115.4689563513026</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407594304485412</v>
+        <v>4.340938208695585</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.658392856651115</v>
+        <v>2.990403507135785</v>
       </c>
       <c r="C2" t="n">
-        <v>9.476810589094461</v>
+        <v>10.47230276120073</v>
       </c>
       <c r="D2" t="n">
-        <v>16.91354944876405</v>
+        <v>22.45747873464579</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.66025854106837</v>
+        <v>7.142214548395545</v>
       </c>
       <c r="C3" t="n">
-        <v>34.23354244708628</v>
+        <v>28.9026524130261</v>
       </c>
       <c r="D3" t="n">
-        <v>41.6899162608408</v>
+        <v>68.00075473465533</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.55096575072749</v>
+        <v>14.4984500963169</v>
       </c>
       <c r="C4" t="n">
-        <v>53.51408561078939</v>
+        <v>51.26784686347268</v>
       </c>
       <c r="D4" t="n">
-        <v>46.91575929054657</v>
+        <v>85.42088599881073</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.243498792849</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="C5" t="n">
-        <v>82.24591392327655</v>
+        <v>82.31954500109507</v>
       </c>
       <c r="D5" t="n">
-        <v>35.66198535676539</v>
+        <v>61.5801247488812</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.84406634594078</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="C6" t="n">
-        <v>97.12724562424971</v>
+        <v>76.5989011284489</v>
       </c>
       <c r="D6" t="n">
-        <v>33.32837106377072</v>
+        <v>43.27053006467818</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>11.31856928226148</v>
       </c>
       <c r="C7" t="n">
-        <v>71.0854060213988</v>
+        <v>39.28561613314036</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>32.71183350550372</v>
+        <v>26.20284622634736</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.26722496866692</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.76190263842031</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.273677405775917</v>
+        <v>18.66287703443404</v>
       </c>
       <c r="C21" t="n">
-        <v>76.37361276064713</v>
+        <v>128.8627223806159</v>
       </c>
       <c r="D21" t="n">
-        <v>5.455258054331938</v>
+        <v>5.332250581266867</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.575525138866883</v>
+        <v>2.610467145592269</v>
       </c>
       <c r="C2" t="n">
-        <v>6.625815255961724</v>
+        <v>6.366633862040565</v>
       </c>
       <c r="D2" t="n">
-        <v>26.64070570244145</v>
+        <v>17.55659419504571</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.36573422979433</v>
+        <v>9.738937226128359</v>
       </c>
       <c r="C3" t="n">
-        <v>35.83869994352981</v>
+        <v>44.23264281484004</v>
       </c>
       <c r="D3" t="n">
-        <v>45.54818473853077</v>
+        <v>76.46832868378407</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.6095107600838</v>
+        <v>9.457175635009525</v>
       </c>
       <c r="C4" t="n">
-        <v>72.49225048158448</v>
+        <v>73.57708169477721</v>
       </c>
       <c r="D4" t="n">
-        <v>57.29185077673112</v>
+        <v>79.42240752586271</v>
       </c>
     </row>
     <row r="5">
@@ -6420,10 +6420,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.25670348136071</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="C5" t="n">
-        <v>91.84249773228912</v>
+        <v>45.74944301790137</v>
       </c>
       <c r="D5" t="n">
         <v>44.17864669110647</v>
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.22270216461057</v>
+        <v>7.003788122096746</v>
       </c>
       <c r="C6" t="n">
-        <v>115.9247689174634</v>
+        <v>25.84156307118455</v>
       </c>
       <c r="D6" t="n">
-        <v>37.43403996293088</v>
+        <v>25.96231803880691</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0676838383308</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>108.4546506358494</v>
+        <v>18.38518925743002</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>66.42504966933919</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>33.17030968338697</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>37.01188845010476</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.482378602292337</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.04735392636186</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.547081277005795</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
